--- a/output/pdf_financials_xlsx/BIR.xlsx
+++ b/output/pdf_financials_xlsx/BIR.xlsx
@@ -2028,13 +2028,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.065</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.046</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.096</v>
       </c>
       <c r="E34" s="1" t="inlineStr">
         <is>
@@ -2120,13 +2120,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.065</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.046</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.096</v>
       </c>
       <c r="E36" s="1" t="inlineStr">
         <is>
@@ -2672,13 +2672,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>2.305</v>
+        <v>2.24</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>2.251</v>
+        <v>2.205</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>2.06</v>
+        <v>1.964</v>
       </c>
       <c r="E48" s="1" t="inlineStr">
         <is>
@@ -29598,7 +29598,7 @@
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E381" s="5" t="n">
